--- a/Packages/cn.etetet.yiuiaudio/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.yiuiaudio/Luban/Config/Base/__enums__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="9167" windowHeight="6540"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>登录2DBGM</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -513,19 +519,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -541,6 +534,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -652,174 +658,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1141,16 +1144,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.8" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="36.125" customWidth="1"/>
-    <col min="3" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="8" width="32.375" customWidth="1"/>
-    <col min="9" max="9" width="24.125" customWidth="1"/>
-    <col min="10" max="12" width="16.875" customWidth="1"/>
-    <col min="13" max="16384" width="7.75" customWidth="1"/>
+    <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.1296296296296" style="1" customWidth="1"/>
+    <col min="3" max="7" width="16.8796296296296" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.3796296296296" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1296296296296" style="1" customWidth="1"/>
+    <col min="10" max="12" width="16.8796296296296" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="7.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1178,10 +1181,10 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1216,7 +1219,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1239,26 +1242,25 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="68" customHeight="1" spans="1:12">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="1" ht="68" customHeight="1" spans="1:12">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="7"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
-      <c r="A5"/>
+    <row r="5" customFormat="1" spans="1:12">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1281,27 +1283,40 @@
       <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
+    <row r="6" customFormat="1" spans="1:12">
       <c r="H6" t="s">
         <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Packages/cn.etetet.yiuiaudio/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.yiuiaudio/Luban/Config/Base/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="9167" windowHeight="6540"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -108,12 +108,6 @@
   </si>
   <si>
     <t>登录2DBGM</t>
-  </si>
-  <si>
-    <t>Test1</t>
-  </si>
-  <si>
-    <t>Test2</t>
   </si>
 </sst>
 </file>
@@ -1144,8 +1138,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.8" outlineLevelRow="7"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.8" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.1296296296296" style="1" customWidth="1"/>
@@ -1300,23 +1294,11 @@
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7"/>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
+      <c r="H7"/>
+      <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
       <c r="L7"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
